--- a/links/links_dex.xlsx
+++ b/links/links_dex.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Links DEX" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Links DEX'!$A$1:$B$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Links DEX'!$A$1:$B$12</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:B12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -495,113 +495,101 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA ATIX S.A.C.</t>
+          <t>DISTRIBUIDORA AURELIO S.A.C.</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>https://OperacionesAdecco.github.io/InformesRutas_DEX/dex/distribuidora-atix-s-a-c.html</t>
+          <t>https://OperacionesAdecco.github.io/InformesRutas_DEX/dex/distribuidora-aurelio-s-a-c.html</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA AURELIO S.A.C.</t>
+          <t>DISTRIBUIDORA CUNZA S.A.</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>https://OperacionesAdecco.github.io/InformesRutas_DEX/dex/distribuidora-aurelio-s-a-c.html</t>
+          <t>https://OperacionesAdecco.github.io/InformesRutas_DEX/dex/distribuidora-cunza-s-a.html</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA CUNZA S.A.</t>
+          <t>DISTRIBUIDORA SOL DEL VALLE S.A.C.</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>https://OperacionesAdecco.github.io/InformesRutas_DEX/dex/distribuidora-cunza-s-a.html</t>
+          <t>https://OperacionesAdecco.github.io/InformesRutas_DEX/dex/distribuidora-sol-del-valle-s-a-c.html</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA SOL DEL VALLE S.A.C.</t>
+          <t>FUERZADEX S.A.C.</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>https://OperacionesAdecco.github.io/InformesRutas_DEX/dex/distribuidora-sol-del-valle-s-a-c.html</t>
+          <t>https://OperacionesAdecco.github.io/InformesRutas_DEX/dex/fuerzadex-s-a-c.html</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>FUERZADEX S.A.C.</t>
+          <t>PACIFICO AYACUCHO</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>https://OperacionesAdecco.github.io/InformesRutas_DEX/dex/fuerzadex-s-a-c.html</t>
+          <t>https://OperacionesAdecco.github.io/InformesRutas_DEX/dex/pacifico-ayacucho.html</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>PACIFICO AYACUCHO</t>
+          <t>PACIFICO DEX SOCIEDAD ANONIMA CERRADA</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>https://OperacionesAdecco.github.io/InformesRutas_DEX/dex/pacifico-ayacucho.html</t>
+          <t>https://OperacionesAdecco.github.io/InformesRutas_DEX/dex/pacifico-dex-sociedad-anonima-cerrada.html</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>PACIFICO DEX SOCIEDAD ANONIMA CERRADA</t>
+          <t>PARDADEX</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>https://OperacionesAdecco.github.io/InformesRutas_DEX/dex/pacifico-dex-sociedad-anonima-cerrada.html</t>
+          <t>https://OperacionesAdecco.github.io/InformesRutas_DEX/dex/pardadex.html</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>PARDADEX</t>
+          <t>ROSET DISTRIBUCIONES EIRL</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>https://OperacionesAdecco.github.io/InformesRutas_DEX/dex/pardadex.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>ROSET DISTRIBUCIONES EIRL</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
           <t>https://OperacionesAdecco.github.io/InformesRutas_DEX/dex/roset-distribuciones-eirl.html</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B13"/>
+  <autoFilter ref="A1:B12"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B3" r:id="rId2"/>
@@ -614,7 +602,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B10" r:id="rId9"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B11" r:id="rId10"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B12" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B13" r:id="rId12"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/links/links_dex.xlsx
+++ b/links/links_dex.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Links DEX" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Links DEX'!$A$1:$B$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Links DEX'!$A$1:$C$12</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:C12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -452,7 +452,12 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Link</t>
+          <t>LinkDashboard</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>LinkImagen</t>
         </is>
       </c>
     </row>
@@ -467,6 +472,11 @@
           <t>https://OperacionesAdecco.github.io/InformesRutas_DEX/dex/atipana-dex-s-a-c.html</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>https://OperacionesAdecco.github.io/InformesRutas_DEX/capturas/atipana-dex-s-a-c.png</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -479,6 +489,11 @@
           <t>https://OperacionesAdecco.github.io/InformesRutas_DEX/dex/atuq-dex-s-a-c.html</t>
         </is>
       </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>https://OperacionesAdecco.github.io/InformesRutas_DEX/capturas/atuq-dex-s-a-c.png</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -491,6 +506,11 @@
           <t>https://OperacionesAdecco.github.io/InformesRutas_DEX/dex/d-l-f-medina-rivera-s-a.html</t>
         </is>
       </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>https://OperacionesAdecco.github.io/InformesRutas_DEX/capturas/d-l-f-medina-rivera-s-a.png</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -503,6 +523,11 @@
           <t>https://OperacionesAdecco.github.io/InformesRutas_DEX/dex/distribuidora-aurelio-s-a-c.html</t>
         </is>
       </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>https://OperacionesAdecco.github.io/InformesRutas_DEX/capturas/distribuidora-aurelio-s-a-c.png</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -515,6 +540,11 @@
           <t>https://OperacionesAdecco.github.io/InformesRutas_DEX/dex/distribuidora-cunza-s-a.html</t>
         </is>
       </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>https://OperacionesAdecco.github.io/InformesRutas_DEX/capturas/distribuidora-cunza-s-a.png</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -527,6 +557,11 @@
           <t>https://OperacionesAdecco.github.io/InformesRutas_DEX/dex/distribuidora-sol-del-valle-s-a-c.html</t>
         </is>
       </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>https://OperacionesAdecco.github.io/InformesRutas_DEX/capturas/distribuidora-sol-del-valle-s-a-c.png</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -539,6 +574,11 @@
           <t>https://OperacionesAdecco.github.io/InformesRutas_DEX/dex/fuerzadex-s-a-c.html</t>
         </is>
       </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>https://OperacionesAdecco.github.io/InformesRutas_DEX/capturas/fuerzadex-s-a-c.png</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -551,6 +591,11 @@
           <t>https://OperacionesAdecco.github.io/InformesRutas_DEX/dex/pacifico-ayacucho.html</t>
         </is>
       </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>https://OperacionesAdecco.github.io/InformesRutas_DEX/capturas/pacifico-ayacucho.png</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -563,6 +608,11 @@
           <t>https://OperacionesAdecco.github.io/InformesRutas_DEX/dex/pacifico-dex-sociedad-anonima-cerrada.html</t>
         </is>
       </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>https://OperacionesAdecco.github.io/InformesRutas_DEX/capturas/pacifico-dex-sociedad-anonima-cerrada.png</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -575,6 +625,11 @@
           <t>https://OperacionesAdecco.github.io/InformesRutas_DEX/dex/pardadex.html</t>
         </is>
       </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>https://OperacionesAdecco.github.io/InformesRutas_DEX/capturas/pardadex.png</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -587,9 +642,14 @@
           <t>https://OperacionesAdecco.github.io/InformesRutas_DEX/dex/roset-distribuciones-eirl.html</t>
         </is>
       </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>https://OperacionesAdecco.github.io/InformesRutas_DEX/capturas/roset-distribuciones-eirl.png</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B12"/>
+  <autoFilter ref="A1:C12"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B3" r:id="rId2"/>
